--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128601851</v>
+        <v>128601893</v>
       </c>
       <c r="B3" t="n">
-        <v>57682</v>
+        <v>79083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446411</v>
+        <v>446344</v>
       </c>
       <c r="R3" t="n">
-        <v>6820425</v>
+        <v>6820395</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128601893</v>
+        <v>128601851</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>57682</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446344</v>
+        <v>446411</v>
       </c>
       <c r="R4" t="n">
-        <v>6820395</v>
+        <v>6820425</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128601857</v>
+        <v>128601860</v>
       </c>
       <c r="B5" t="n">
-        <v>57845</v>
+        <v>57682</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1007,7 +1007,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446472</v>
+        <v>446460</v>
       </c>
       <c r="R5" t="n">
         <v>6820443</v>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128601860</v>
+        <v>128601857</v>
       </c>
       <c r="B7" t="n">
-        <v>57682</v>
+        <v>57845</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446460</v>
+        <v>446472</v>
       </c>
       <c r="R7" t="n">
         <v>6820443</v>
@@ -1572,32 +1572,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128601920</v>
+        <v>128601887</v>
       </c>
       <c r="B11" t="n">
-        <v>92776</v>
+        <v>79083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446382</v>
+        <v>446262</v>
       </c>
       <c r="R11" t="n">
-        <v>6820411</v>
+        <v>6820239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,7 +1651,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1670,32 +1669,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128601887</v>
+        <v>128601920</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>92776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1704,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446262</v>
+        <v>446382</v>
       </c>
       <c r="R12" t="n">
-        <v>6820239</v>
+        <v>6820411</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1749,6 +1748,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2836,6 +2836,107 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128629754</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58055</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>446411</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6820425</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128601884</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128601893</v>
+        <v>128601851</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>57686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446344</v>
+        <v>446411</v>
       </c>
       <c r="R3" t="n">
-        <v>6820395</v>
+        <v>6820425</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128601851</v>
+        <v>128601893</v>
       </c>
       <c r="B4" t="n">
-        <v>57682</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446411</v>
+        <v>446344</v>
       </c>
       <c r="R4" t="n">
-        <v>6820425</v>
+        <v>6820395</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128601860</v>
+        <v>128601889</v>
       </c>
       <c r="B5" t="n">
-        <v>57682</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,42 +985,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446460</v>
+        <v>446292</v>
       </c>
       <c r="R5" t="n">
-        <v>6820443</v>
+        <v>6820252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128601889</v>
+        <v>128601860</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>57686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,34 +1082,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446292</v>
+        <v>446460</v>
       </c>
       <c r="R6" t="n">
-        <v>6820252</v>
+        <v>6820443</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>128601857</v>
       </c>
       <c r="B7" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128601875</v>
       </c>
       <c r="B8" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>128601894</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128601886</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,32 +1572,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128601887</v>
+        <v>128601920</v>
       </c>
       <c r="B11" t="n">
-        <v>79083</v>
+        <v>92782</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446262</v>
+        <v>446382</v>
       </c>
       <c r="R11" t="n">
-        <v>6820239</v>
+        <v>6820411</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,6 +1651,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1669,32 +1670,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128601920</v>
+        <v>128601887</v>
       </c>
       <c r="B12" t="n">
-        <v>92776</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1704,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446382</v>
+        <v>446262</v>
       </c>
       <c r="R12" t="n">
-        <v>6820411</v>
+        <v>6820239</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,7 +1749,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>128601872</v>
       </c>
       <c r="B13" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128601895</v>
+        <v>128601883</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446389</v>
+        <v>446146</v>
       </c>
       <c r="R14" t="n">
-        <v>6820420</v>
+        <v>6820335</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1961,10 +1961,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128601883</v>
+        <v>128601895</v>
       </c>
       <c r="B15" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446146</v>
+        <v>446389</v>
       </c>
       <c r="R15" t="n">
-        <v>6820335</v>
+        <v>6820420</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2061,7 +2061,7 @@
         <v>128605463</v>
       </c>
       <c r="B16" t="n">
-        <v>92149</v>
+        <v>92155</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>128601891</v>
       </c>
       <c r="B17" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>128601896</v>
       </c>
       <c r="B18" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>128601885</v>
       </c>
       <c r="B19" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>128601890</v>
       </c>
       <c r="B20" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>128601888</v>
       </c>
       <c r="B21" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>128601892</v>
       </c>
       <c r="B22" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>128601868</v>
       </c>
       <c r="B23" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>128629754</v>
       </c>
       <c r="B24" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128601889</v>
+        <v>128601860</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,34 +985,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446292</v>
+        <v>446460</v>
       </c>
       <c r="R5" t="n">
-        <v>6820252</v>
+        <v>6820443</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128601860</v>
+        <v>128601889</v>
       </c>
       <c r="B6" t="n">
-        <v>57686</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,42 +1090,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446460</v>
+        <v>446292</v>
       </c>
       <c r="R6" t="n">
-        <v>6820443</v>
+        <v>6820252</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1572,32 +1572,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128601920</v>
+        <v>128601887</v>
       </c>
       <c r="B11" t="n">
-        <v>92782</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446382</v>
+        <v>446262</v>
       </c>
       <c r="R11" t="n">
-        <v>6820411</v>
+        <v>6820239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,7 +1651,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1670,32 +1669,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128601887</v>
+        <v>128601920</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>92788</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1704,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446262</v>
+        <v>446382</v>
       </c>
       <c r="R12" t="n">
-        <v>6820239</v>
+        <v>6820411</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1749,6 +1748,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128601883</v>
+        <v>128601895</v>
       </c>
       <c r="B14" t="n">
         <v>79087</v>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446146</v>
+        <v>446389</v>
       </c>
       <c r="R14" t="n">
-        <v>6820335</v>
+        <v>6820420</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1961,7 +1961,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128601895</v>
+        <v>128601883</v>
       </c>
       <c r="B15" t="n">
         <v>79087</v>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446389</v>
+        <v>446146</v>
       </c>
       <c r="R15" t="n">
-        <v>6820420</v>
+        <v>6820335</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2061,7 +2061,7 @@
         <v>128605463</v>
       </c>
       <c r="B16" t="n">
-        <v>92155</v>
+        <v>92161</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>128601868</v>
       </c>
       <c r="B23" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128601860</v>
+        <v>128601889</v>
       </c>
       <c r="B5" t="n">
-        <v>57686</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,42 +985,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446460</v>
+        <v>446292</v>
       </c>
       <c r="R5" t="n">
-        <v>6820443</v>
+        <v>6820252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128601889</v>
+        <v>128601860</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,34 +1082,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446292</v>
+        <v>446460</v>
       </c>
       <c r="R6" t="n">
-        <v>6820252</v>
+        <v>6820443</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1572,32 +1572,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128601887</v>
+        <v>128601920</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>92788</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446262</v>
+        <v>446382</v>
       </c>
       <c r="R11" t="n">
-        <v>6820239</v>
+        <v>6820411</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,6 +1651,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1669,32 +1670,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128601920</v>
+        <v>128601887</v>
       </c>
       <c r="B12" t="n">
-        <v>92788</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1704,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446382</v>
+        <v>446262</v>
       </c>
       <c r="R12" t="n">
-        <v>6820411</v>
+        <v>6820239</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,7 +1749,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128601884</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128601851</v>
+        <v>128601893</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446411</v>
+        <v>446344</v>
       </c>
       <c r="R3" t="n">
-        <v>6820425</v>
+        <v>6820395</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128601893</v>
+        <v>128601851</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446344</v>
+        <v>446411</v>
       </c>
       <c r="R4" t="n">
-        <v>6820395</v>
+        <v>6820425</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128601889</v>
+        <v>128601860</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,34 +985,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446292</v>
+        <v>446460</v>
       </c>
       <c r="R5" t="n">
-        <v>6820252</v>
+        <v>6820443</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128601860</v>
+        <v>128601857</v>
       </c>
       <c r="B6" t="n">
-        <v>57686</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1104,7 +1112,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1114,7 +1122,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446460</v>
+        <v>446472</v>
       </c>
       <c r="R6" t="n">
         <v>6820443</v>
@@ -1176,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128601857</v>
+        <v>128601889</v>
       </c>
       <c r="B7" t="n">
-        <v>57849</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,42 +1195,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446472</v>
+        <v>446292</v>
       </c>
       <c r="R7" t="n">
-        <v>6820443</v>
+        <v>6820252</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,7 +1284,7 @@
         <v>128601875</v>
       </c>
       <c r="B8" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>128601894</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128601886</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128601920</v>
       </c>
       <c r="B11" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>128601887</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>128601872</v>
       </c>
       <c r="B13" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>128601895</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>128601883</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>128605463</v>
       </c>
       <c r="B16" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>128601891</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>128601896</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>128601885</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>128601890</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>128601888</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>128601892</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>128601868</v>
       </c>
       <c r="B23" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128601893</v>
+        <v>128601851</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446344</v>
+        <v>446411</v>
       </c>
       <c r="R3" t="n">
-        <v>6820395</v>
+        <v>6820425</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128601851</v>
+        <v>128601893</v>
       </c>
       <c r="B4" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446411</v>
+        <v>446344</v>
       </c>
       <c r="R4" t="n">
-        <v>6820425</v>
+        <v>6820395</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128601860</v>
+        <v>128601889</v>
       </c>
       <c r="B5" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,42 +985,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446460</v>
+        <v>446292</v>
       </c>
       <c r="R5" t="n">
-        <v>6820443</v>
+        <v>6820252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128601857</v>
+        <v>128601860</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1112,7 +1104,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1122,7 +1114,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446472</v>
+        <v>446460</v>
       </c>
       <c r="R6" t="n">
         <v>6820443</v>
@@ -1184,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128601889</v>
+        <v>128601857</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>57849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,34 +1187,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446292</v>
+        <v>446472</v>
       </c>
       <c r="R7" t="n">
-        <v>6820252</v>
+        <v>6820443</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2353,7 +2353,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128601885</v>
+        <v>128601890</v>
       </c>
       <c r="B19" t="n">
         <v>79089</v>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446180</v>
+        <v>446320</v>
       </c>
       <c r="R19" t="n">
-        <v>6820275</v>
+        <v>6820391</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2450,7 +2450,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128601890</v>
+        <v>128601885</v>
       </c>
       <c r="B20" t="n">
         <v>79089</v>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446320</v>
+        <v>446180</v>
       </c>
       <c r="R20" t="n">
-        <v>6820391</v>
+        <v>6820275</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128601889</v>
+        <v>128601860</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,34 +985,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446292</v>
+        <v>446460</v>
       </c>
       <c r="R5" t="n">
-        <v>6820252</v>
+        <v>6820443</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128601860</v>
+        <v>128601857</v>
       </c>
       <c r="B6" t="n">
-        <v>57686</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1104,7 +1112,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1114,7 +1122,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446460</v>
+        <v>446472</v>
       </c>
       <c r="R6" t="n">
         <v>6820443</v>
@@ -1176,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128601857</v>
+        <v>128601889</v>
       </c>
       <c r="B7" t="n">
-        <v>57849</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,42 +1195,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446472</v>
+        <v>446292</v>
       </c>
       <c r="R7" t="n">
-        <v>6820443</v>
+        <v>6820252</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2450,7 +2450,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128601885</v>
+        <v>128601888</v>
       </c>
       <c r="B20" t="n">
         <v>79089</v>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446180</v>
+        <v>446265</v>
       </c>
       <c r="R20" t="n">
-        <v>6820275</v>
+        <v>6820246</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,7 +2547,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128601888</v>
+        <v>128601885</v>
       </c>
       <c r="B21" t="n">
         <v>79089</v>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446265</v>
+        <v>446180</v>
       </c>
       <c r="R21" t="n">
-        <v>6820246</v>
+        <v>6820275</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128601860</v>
+        <v>128601857</v>
       </c>
       <c r="B5" t="n">
-        <v>57686</v>
+        <v>57849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1007,7 +1007,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446460</v>
+        <v>446472</v>
       </c>
       <c r="R5" t="n">
         <v>6820443</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128601857</v>
+        <v>128601889</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,42 +1090,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446472</v>
+        <v>446292</v>
       </c>
       <c r="R6" t="n">
-        <v>6820443</v>
+        <v>6820252</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128601889</v>
+        <v>128601860</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,34 +1187,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446292</v>
+        <v>446460</v>
       </c>
       <c r="R7" t="n">
-        <v>6820252</v>
+        <v>6820443</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1572,32 +1572,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128601920</v>
+        <v>128601887</v>
       </c>
       <c r="B11" t="n">
-        <v>92790</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446382</v>
+        <v>446262</v>
       </c>
       <c r="R11" t="n">
-        <v>6820411</v>
+        <v>6820239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,7 +1651,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1670,32 +1669,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128601887</v>
+        <v>128601920</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>92791</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1704,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446262</v>
+        <v>446382</v>
       </c>
       <c r="R12" t="n">
-        <v>6820239</v>
+        <v>6820411</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1749,6 +1748,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>128605463</v>
       </c>
       <c r="B16" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128601890</v>
+        <v>128601885</v>
       </c>
       <c r="B19" t="n">
         <v>79089</v>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446320</v>
+        <v>446180</v>
       </c>
       <c r="R19" t="n">
-        <v>6820391</v>
+        <v>6820275</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2450,7 +2450,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128601888</v>
+        <v>128601890</v>
       </c>
       <c r="B20" t="n">
         <v>79089</v>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446265</v>
+        <v>446320</v>
       </c>
       <c r="R20" t="n">
-        <v>6820246</v>
+        <v>6820391</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,7 +2547,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128601885</v>
+        <v>128601888</v>
       </c>
       <c r="B21" t="n">
         <v>79089</v>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446180</v>
+        <v>446265</v>
       </c>
       <c r="R21" t="n">
-        <v>6820275</v>
+        <v>6820246</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
         <v>128601868</v>
       </c>
       <c r="B23" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128601884</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128601851</v>
+        <v>128601893</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446411</v>
+        <v>446344</v>
       </c>
       <c r="R3" t="n">
-        <v>6820425</v>
+        <v>6820395</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128601893</v>
+        <v>128601851</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>57713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446344</v>
+        <v>446411</v>
       </c>
       <c r="R4" t="n">
-        <v>6820395</v>
+        <v>6820425</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128601857</v>
+        <v>128601889</v>
       </c>
       <c r="B5" t="n">
-        <v>57849</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,42 +985,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446472</v>
+        <v>446292</v>
       </c>
       <c r="R5" t="n">
-        <v>6820443</v>
+        <v>6820252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128601889</v>
+        <v>128601860</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>57713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,34 +1082,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446292</v>
+        <v>446460</v>
       </c>
       <c r="R6" t="n">
-        <v>6820252</v>
+        <v>6820443</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128601860</v>
+        <v>128601857</v>
       </c>
       <c r="B7" t="n">
-        <v>57686</v>
+        <v>57876</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446460</v>
+        <v>446472</v>
       </c>
       <c r="R7" t="n">
         <v>6820443</v>
@@ -1284,7 +1284,7 @@
         <v>128601875</v>
       </c>
       <c r="B8" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>128601894</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128601886</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128601887</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>128601920</v>
       </c>
       <c r="B12" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>128601872</v>
       </c>
       <c r="B13" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128601895</v>
+        <v>128601883</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446389</v>
+        <v>446146</v>
       </c>
       <c r="R14" t="n">
-        <v>6820420</v>
+        <v>6820335</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1961,10 +1961,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128601883</v>
+        <v>128601895</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446146</v>
+        <v>446389</v>
       </c>
       <c r="R15" t="n">
-        <v>6820335</v>
+        <v>6820420</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2061,7 +2061,7 @@
         <v>128605463</v>
       </c>
       <c r="B16" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>128601891</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>128601896</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>128601885</v>
       </c>
       <c r="B19" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>128601890</v>
       </c>
       <c r="B20" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>128601888</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>128601892</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>128601868</v>
       </c>
       <c r="B23" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>128629754</v>
       </c>
       <c r="B24" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128601884</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128601893</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>128601889</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128601875</v>
       </c>
       <c r="B8" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>128601894</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128601886</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128601887</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>128601920</v>
       </c>
       <c r="B12" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>128601872</v>
       </c>
       <c r="B13" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128601883</v>
+        <v>128601895</v>
       </c>
       <c r="B14" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446146</v>
+        <v>446389</v>
       </c>
       <c r="R14" t="n">
-        <v>6820335</v>
+        <v>6820420</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1961,10 +1961,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128601895</v>
+        <v>128601883</v>
       </c>
       <c r="B15" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446389</v>
+        <v>446146</v>
       </c>
       <c r="R15" t="n">
-        <v>6820420</v>
+        <v>6820335</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2061,7 +2061,7 @@
         <v>128605463</v>
       </c>
       <c r="B16" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>128601891</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>128601896</v>
       </c>
       <c r="B18" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>128601885</v>
       </c>
       <c r="B19" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>128601890</v>
       </c>
       <c r="B20" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>128601888</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>128601892</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>128601868</v>
       </c>
       <c r="B23" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128601889</v>
+        <v>128601860</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,34 +985,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446292</v>
+        <v>446460</v>
       </c>
       <c r="R5" t="n">
-        <v>6820252</v>
+        <v>6820443</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128601860</v>
+        <v>128601889</v>
       </c>
       <c r="B6" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,42 +1090,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446460</v>
+        <v>446292</v>
       </c>
       <c r="R6" t="n">
-        <v>6820443</v>
+        <v>6820252</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1572,32 +1572,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128601887</v>
+        <v>128601920</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>92830</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446262</v>
+        <v>446382</v>
       </c>
       <c r="R11" t="n">
-        <v>6820239</v>
+        <v>6820411</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,6 +1651,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1669,32 +1670,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128601920</v>
+        <v>128601887</v>
       </c>
       <c r="B12" t="n">
-        <v>92823</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1704,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446382</v>
+        <v>446262</v>
       </c>
       <c r="R12" t="n">
-        <v>6820411</v>
+        <v>6820239</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,7 +1749,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>128605463</v>
       </c>
       <c r="B16" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>128601868</v>
       </c>
       <c r="B23" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128601893</v>
+        <v>128601851</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446344</v>
+        <v>446411</v>
       </c>
       <c r="R3" t="n">
-        <v>6820395</v>
+        <v>6820425</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128601851</v>
+        <v>128601893</v>
       </c>
       <c r="B4" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446411</v>
+        <v>446344</v>
       </c>
       <c r="R4" t="n">
-        <v>6820425</v>
+        <v>6820395</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1572,32 +1572,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128601920</v>
+        <v>128601887</v>
       </c>
       <c r="B11" t="n">
-        <v>92830</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446382</v>
+        <v>446262</v>
       </c>
       <c r="R11" t="n">
-        <v>6820411</v>
+        <v>6820239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,7 +1651,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1670,32 +1669,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128601887</v>
+        <v>128601920</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>92830</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1704,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446262</v>
+        <v>446382</v>
       </c>
       <c r="R12" t="n">
-        <v>6820239</v>
+        <v>6820411</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1749,6 +1748,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128601851</v>
+        <v>128601893</v>
       </c>
       <c r="B3" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446411</v>
+        <v>446344</v>
       </c>
       <c r="R3" t="n">
-        <v>6820425</v>
+        <v>6820395</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128601893</v>
+        <v>128601851</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446344</v>
+        <v>446411</v>
       </c>
       <c r="R4" t="n">
-        <v>6820395</v>
+        <v>6820425</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128601860</v>
+        <v>128601857</v>
       </c>
       <c r="B5" t="n">
-        <v>57713</v>
+        <v>57876</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1007,7 +1007,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446460</v>
+        <v>446472</v>
       </c>
       <c r="R5" t="n">
         <v>6820443</v>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128601857</v>
+        <v>128601860</v>
       </c>
       <c r="B7" t="n">
-        <v>57876</v>
+        <v>57713</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446472</v>
+        <v>446460</v>
       </c>
       <c r="R7" t="n">
         <v>6820443</v>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128601884</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128601893</v>
+        <v>128601851</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>57717</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446344</v>
+        <v>446411</v>
       </c>
       <c r="R3" t="n">
-        <v>6820395</v>
+        <v>6820425</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128601851</v>
+        <v>128601893</v>
       </c>
       <c r="B4" t="n">
-        <v>57713</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446411</v>
+        <v>446344</v>
       </c>
       <c r="R4" t="n">
-        <v>6820425</v>
+        <v>6820395</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
         <v>128601857</v>
       </c>
       <c r="B5" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>128601889</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>128601860</v>
       </c>
       <c r="B7" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128601875</v>
       </c>
       <c r="B8" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>128601894</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128601886</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,32 +1572,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128601887</v>
+        <v>128601920</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>92834</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446262</v>
+        <v>446382</v>
       </c>
       <c r="R11" t="n">
-        <v>6820239</v>
+        <v>6820411</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,6 +1651,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1669,32 +1670,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128601920</v>
+        <v>128601887</v>
       </c>
       <c r="B12" t="n">
-        <v>92830</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1704,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446382</v>
+        <v>446262</v>
       </c>
       <c r="R12" t="n">
-        <v>6820411</v>
+        <v>6820239</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,7 +1749,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>128601872</v>
       </c>
       <c r="B13" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>128601895</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>128601883</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>128605463</v>
       </c>
       <c r="B16" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>128601891</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>128601896</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>128601885</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>128601890</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>128601888</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>128601892</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>128601868</v>
       </c>
       <c r="B23" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>128629754</v>
       </c>
       <c r="B24" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128601857</v>
+        <v>128601860</v>
       </c>
       <c r="B5" t="n">
-        <v>57880</v>
+        <v>57717</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1007,7 +1007,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446472</v>
+        <v>446460</v>
       </c>
       <c r="R5" t="n">
         <v>6820443</v>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128601860</v>
+        <v>128601857</v>
       </c>
       <c r="B7" t="n">
-        <v>57717</v>
+        <v>57880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446460</v>
+        <v>446472</v>
       </c>
       <c r="R7" t="n">
         <v>6820443</v>
@@ -1572,32 +1572,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128601920</v>
+        <v>128601887</v>
       </c>
       <c r="B11" t="n">
-        <v>92834</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446382</v>
+        <v>446262</v>
       </c>
       <c r="R11" t="n">
-        <v>6820411</v>
+        <v>6820239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,7 +1651,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1670,32 +1669,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128601887</v>
+        <v>128601920</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>92834</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1704,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446262</v>
+        <v>446382</v>
       </c>
       <c r="R12" t="n">
-        <v>6820239</v>
+        <v>6820411</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1749,6 +1748,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128601860</v>
+        <v>128601889</v>
       </c>
       <c r="B5" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,42 +985,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446460</v>
+        <v>446292</v>
       </c>
       <c r="R5" t="n">
-        <v>6820443</v>
+        <v>6820252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128601889</v>
+        <v>128601860</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,34 +1082,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446292</v>
+        <v>446460</v>
       </c>
       <c r="R6" t="n">
-        <v>6820252</v>
+        <v>6820443</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2353,7 +2353,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128601885</v>
+        <v>128601890</v>
       </c>
       <c r="B19" t="n">
         <v>79124</v>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446180</v>
+        <v>446320</v>
       </c>
       <c r="R19" t="n">
-        <v>6820275</v>
+        <v>6820391</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2450,7 +2450,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128601890</v>
+        <v>128601885</v>
       </c>
       <c r="B20" t="n">
         <v>79124</v>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446320</v>
+        <v>446180</v>
       </c>
       <c r="R20" t="n">
-        <v>6820391</v>
+        <v>6820275</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128601884</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128601851</v>
       </c>
       <c r="B3" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>128601893</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>128601889</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>128601860</v>
       </c>
       <c r="B6" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>128601857</v>
       </c>
       <c r="B7" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128601875</v>
       </c>
       <c r="B8" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>128601894</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128601886</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,32 +1572,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128601887</v>
+        <v>128601920</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>92839</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446262</v>
+        <v>446382</v>
       </c>
       <c r="R11" t="n">
-        <v>6820239</v>
+        <v>6820411</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,6 +1651,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1669,32 +1670,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128601920</v>
+        <v>128601887</v>
       </c>
       <c r="B12" t="n">
-        <v>92834</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1704,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446382</v>
+        <v>446262</v>
       </c>
       <c r="R12" t="n">
-        <v>6820411</v>
+        <v>6820239</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,7 +1749,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>128601872</v>
       </c>
       <c r="B13" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>128601895</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>128601883</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>128605463</v>
       </c>
       <c r="B16" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>128601891</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>128601896</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>128601890</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2450,10 +2450,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128601885</v>
+        <v>128601888</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446180</v>
+        <v>446265</v>
       </c>
       <c r="R20" t="n">
-        <v>6820275</v>
+        <v>6820246</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,10 +2547,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128601888</v>
+        <v>128601885</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446265</v>
+        <v>446180</v>
       </c>
       <c r="R21" t="n">
-        <v>6820246</v>
+        <v>6820275</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2647,7 +2647,7 @@
         <v>128601892</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>128601868</v>
       </c>
       <c r="B23" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>128629754</v>
       </c>
       <c r="B24" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128601884</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128601851</v>
+        <v>128601893</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446411</v>
+        <v>446344</v>
       </c>
       <c r="R3" t="n">
-        <v>6820425</v>
+        <v>6820395</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128601893</v>
+        <v>128601851</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446344</v>
+        <v>446411</v>
       </c>
       <c r="R4" t="n">
-        <v>6820395</v>
+        <v>6820425</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128601860</v>
+        <v>128601857</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1007,7 +1007,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446460</v>
+        <v>446472</v>
       </c>
       <c r="R5" t="n">
         <v>6820443</v>
@@ -1082,7 +1082,7 @@
         <v>128601889</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128601857</v>
+        <v>128601860</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446472</v>
+        <v>446460</v>
       </c>
       <c r="R7" t="n">
         <v>6820443</v>
@@ -1284,7 +1284,7 @@
         <v>128601875</v>
       </c>
       <c r="B8" t="n">
-        <v>78786</v>
+        <v>78791</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>128601894</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128601886</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128601920</v>
       </c>
       <c r="B11" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>128601887</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>128601872</v>
       </c>
       <c r="B13" t="n">
-        <v>78787</v>
+        <v>78792</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>128601895</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>128601883</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>128605463</v>
       </c>
       <c r="B16" t="n">
-        <v>92213</v>
+        <v>92218</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>128601891</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>128601896</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128601890</v>
+        <v>128601885</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446320</v>
+        <v>446180</v>
       </c>
       <c r="R19" t="n">
-        <v>6820391</v>
+        <v>6820275</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2450,10 +2450,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128601885</v>
+        <v>128601890</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446180</v>
+        <v>446320</v>
       </c>
       <c r="R20" t="n">
-        <v>6820275</v>
+        <v>6820391</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2550,7 +2550,7 @@
         <v>128601888</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>128601892</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>128601868</v>
       </c>
       <c r="B23" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128601893</v>
+        <v>128601851</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446344</v>
+        <v>446411</v>
       </c>
       <c r="R3" t="n">
-        <v>6820395</v>
+        <v>6820425</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128601851</v>
+        <v>128601893</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446411</v>
+        <v>446344</v>
       </c>
       <c r="R4" t="n">
-        <v>6820425</v>
+        <v>6820395</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128601857</v>
+        <v>128601860</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1007,7 +1007,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446472</v>
+        <v>446460</v>
       </c>
       <c r="R5" t="n">
         <v>6820443</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128601889</v>
+        <v>128601857</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>57883</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,34 +1090,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446292</v>
+        <v>446472</v>
       </c>
       <c r="R6" t="n">
-        <v>6820252</v>
+        <v>6820443</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128601860</v>
+        <v>128601889</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,42 +1195,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446460</v>
+        <v>446292</v>
       </c>
       <c r="R7" t="n">
-        <v>6820443</v>
+        <v>6820252</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128601884</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128601851</v>
+        <v>128601893</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446411</v>
+        <v>446344</v>
       </c>
       <c r="R3" t="n">
-        <v>6820425</v>
+        <v>6820395</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128601893</v>
+        <v>128601851</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446344</v>
+        <v>446411</v>
       </c>
       <c r="R4" t="n">
-        <v>6820395</v>
+        <v>6820425</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128601860</v>
+        <v>128601889</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,42 +985,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446460</v>
+        <v>446292</v>
       </c>
       <c r="R5" t="n">
-        <v>6820443</v>
+        <v>6820252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128601857</v>
+        <v>128601860</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1112,7 +1104,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1122,7 +1114,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446472</v>
+        <v>446460</v>
       </c>
       <c r="R6" t="n">
         <v>6820443</v>
@@ -1184,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128601889</v>
+        <v>128601857</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,34 +1187,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446292</v>
+        <v>446472</v>
       </c>
       <c r="R7" t="n">
-        <v>6820252</v>
+        <v>6820443</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,7 +1284,7 @@
         <v>128601875</v>
       </c>
       <c r="B8" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>128601894</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128601886</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,32 +1572,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128601920</v>
+        <v>128601887</v>
       </c>
       <c r="B11" t="n">
-        <v>92847</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446382</v>
+        <v>446262</v>
       </c>
       <c r="R11" t="n">
-        <v>6820411</v>
+        <v>6820239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,7 +1651,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1670,32 +1669,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128601887</v>
+        <v>128601920</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>92855</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1704,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446262</v>
+        <v>446382</v>
       </c>
       <c r="R12" t="n">
-        <v>6820239</v>
+        <v>6820411</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1749,6 +1748,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>128601872</v>
       </c>
       <c r="B13" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>128601895</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>128601883</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>128605463</v>
       </c>
       <c r="B16" t="n">
-        <v>92218</v>
+        <v>92226</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>128601891</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>128601896</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>128601885</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>128601890</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>128601888</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>128601892</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>128601868</v>
       </c>
       <c r="B23" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2937,6 +2937,1504 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129129058</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92819</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>446229</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6820293</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129129032</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>446248</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6820316</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129128610</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>185</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>446203</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6820289</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129128613</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>185</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>446138</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6820318</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129128612</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>185</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>446140</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6820308</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129129039</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>446149</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6820301</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129129041</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>446136</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6820317</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129129035</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>446187</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6820278</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129128611</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>185</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>446149</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6820301</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129129034</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>446210</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6820287</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129129031</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>446212</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6820334</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129129036</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>446191</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6820271</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129129038</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>446182</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6820270</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129129040</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>446141</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6820307</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128601893</v>
+        <v>128601851</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446344</v>
+        <v>446411</v>
       </c>
       <c r="R3" t="n">
-        <v>6820395</v>
+        <v>6820425</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128601851</v>
+        <v>128601893</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446411</v>
+        <v>446344</v>
       </c>
       <c r="R4" t="n">
-        <v>6820425</v>
+        <v>6820395</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1572,32 +1572,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128601887</v>
+        <v>128601920</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>92855</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446262</v>
+        <v>446382</v>
       </c>
       <c r="R11" t="n">
-        <v>6820239</v>
+        <v>6820411</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,6 +1651,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1669,32 +1670,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128601920</v>
+        <v>128601887</v>
       </c>
       <c r="B12" t="n">
-        <v>92855</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1704,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446382</v>
+        <v>446262</v>
       </c>
       <c r="R12" t="n">
-        <v>6820411</v>
+        <v>6820239</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,7 +1749,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -3260,7 +3260,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129128613</v>
+        <v>129128612</v>
       </c>
       <c r="B28" t="n">
         <v>79067</v>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446138</v>
+        <v>446140</v>
       </c>
       <c r="R28" t="n">
-        <v>6820318</v>
+        <v>6820308</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3367,7 +3367,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129128612</v>
+        <v>129128613</v>
       </c>
       <c r="B29" t="n">
         <v>79067</v>
@@ -3402,10 +3402,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446140</v>
+        <v>446138</v>
       </c>
       <c r="R29" t="n">
-        <v>6820308</v>
+        <v>6820318</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129129034</v>
+        <v>129129031</v>
       </c>
       <c r="B34" t="n">
         <v>79035</v>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446210</v>
+        <v>446212</v>
       </c>
       <c r="R34" t="n">
-        <v>6820287</v>
+        <v>6820334</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4009,7 +4009,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129129031</v>
+        <v>129129034</v>
       </c>
       <c r="B35" t="n">
         <v>79035</v>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446212</v>
+        <v>446210</v>
       </c>
       <c r="R35" t="n">
-        <v>6820334</v>
+        <v>6820287</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -3902,7 +3902,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129129031</v>
+        <v>129129034</v>
       </c>
       <c r="B34" t="n">
         <v>79035</v>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446212</v>
+        <v>446210</v>
       </c>
       <c r="R34" t="n">
-        <v>6820334</v>
+        <v>6820287</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4009,7 +4009,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129129034</v>
+        <v>129129036</v>
       </c>
       <c r="B35" t="n">
         <v>79035</v>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446210</v>
+        <v>446191</v>
       </c>
       <c r="R35" t="n">
-        <v>6820287</v>
+        <v>6820271</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4116,7 +4116,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129129036</v>
+        <v>129129038</v>
       </c>
       <c r="B36" t="n">
         <v>79035</v>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446191</v>
+        <v>446182</v>
       </c>
       <c r="R36" t="n">
-        <v>6820271</v>
+        <v>6820270</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4223,7 +4223,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129129038</v>
+        <v>129129040</v>
       </c>
       <c r="B37" t="n">
         <v>79035</v>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446182</v>
+        <v>446141</v>
       </c>
       <c r="R37" t="n">
-        <v>6820270</v>
+        <v>6820307</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4330,7 +4330,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129129040</v>
+        <v>129129031</v>
       </c>
       <c r="B38" t="n">
         <v>79035</v>
@@ -4365,10 +4365,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446141</v>
+        <v>446212</v>
       </c>
       <c r="R38" t="n">
-        <v>6820307</v>
+        <v>6820334</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -2841,7 +2841,7 @@
         <v>128629754</v>
       </c>
       <c r="B24" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>129129058</v>
       </c>
       <c r="B25" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>129129032</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>129128610</v>
       </c>
       <c r="B27" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>129128612</v>
       </c>
       <c r="B28" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>129128613</v>
       </c>
       <c r="B29" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>129129039</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>129129041</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>129129035</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>129128611</v>
       </c>
       <c r="B33" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129129034</v>
+        <v>129129040</v>
       </c>
       <c r="B34" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446210</v>
+        <v>446141</v>
       </c>
       <c r="R34" t="n">
-        <v>6820287</v>
+        <v>6820307</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4009,10 +4009,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129129036</v>
+        <v>129129031</v>
       </c>
       <c r="B35" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446191</v>
+        <v>446212</v>
       </c>
       <c r="R35" t="n">
-        <v>6820271</v>
+        <v>6820334</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4116,10 +4116,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129129038</v>
+        <v>129129034</v>
       </c>
       <c r="B36" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446182</v>
+        <v>446210</v>
       </c>
       <c r="R36" t="n">
-        <v>6820270</v>
+        <v>6820287</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4223,10 +4223,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129129040</v>
+        <v>129129038</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446141</v>
+        <v>446182</v>
       </c>
       <c r="R37" t="n">
-        <v>6820307</v>
+        <v>6820270</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4330,10 +4330,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129129031</v>
+        <v>129129036</v>
       </c>
       <c r="B38" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4365,10 +4365,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446212</v>
+        <v>446191</v>
       </c>
       <c r="R38" t="n">
-        <v>6820334</v>
+        <v>6820271</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -3902,7 +3902,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129129040</v>
+        <v>129129036</v>
       </c>
       <c r="B34" t="n">
         <v>79039</v>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446141</v>
+        <v>446191</v>
       </c>
       <c r="R34" t="n">
-        <v>6820307</v>
+        <v>6820271</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4009,7 +4009,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129129031</v>
+        <v>129129040</v>
       </c>
       <c r="B35" t="n">
         <v>79039</v>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446212</v>
+        <v>446141</v>
       </c>
       <c r="R35" t="n">
-        <v>6820334</v>
+        <v>6820307</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4116,7 +4116,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129129034</v>
+        <v>129129031</v>
       </c>
       <c r="B36" t="n">
         <v>79039</v>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446210</v>
+        <v>446212</v>
       </c>
       <c r="R36" t="n">
-        <v>6820287</v>
+        <v>6820334</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4223,7 +4223,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129129038</v>
+        <v>129129034</v>
       </c>
       <c r="B37" t="n">
         <v>79039</v>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446182</v>
+        <v>446210</v>
       </c>
       <c r="R37" t="n">
-        <v>6820270</v>
+        <v>6820287</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4330,7 +4330,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129129036</v>
+        <v>129129038</v>
       </c>
       <c r="B38" t="n">
         <v>79039</v>
@@ -4365,10 +4365,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446191</v>
+        <v>446182</v>
       </c>
       <c r="R38" t="n">
-        <v>6820271</v>
+        <v>6820270</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -2942,7 +2942,7 @@
         <v>129129058</v>
       </c>
       <c r="B25" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129129036</v>
+        <v>129129040</v>
       </c>
       <c r="B34" t="n">
         <v>79039</v>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446191</v>
+        <v>446141</v>
       </c>
       <c r="R34" t="n">
-        <v>6820271</v>
+        <v>6820307</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4009,7 +4009,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129129040</v>
+        <v>129129034</v>
       </c>
       <c r="B35" t="n">
         <v>79039</v>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446141</v>
+        <v>446210</v>
       </c>
       <c r="R35" t="n">
-        <v>6820307</v>
+        <v>6820287</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4223,7 +4223,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129129034</v>
+        <v>129129036</v>
       </c>
       <c r="B37" t="n">
         <v>79039</v>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446210</v>
+        <v>446191</v>
       </c>
       <c r="R37" t="n">
-        <v>6820287</v>
+        <v>6820271</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -2942,7 +2942,7 @@
         <v>129129058</v>
       </c>
       <c r="B25" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>129129032</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>129128610</v>
       </c>
       <c r="B27" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>129128612</v>
       </c>
       <c r="B28" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>129128613</v>
       </c>
       <c r="B29" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>129129039</v>
       </c>
       <c r="B30" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>129129041</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>129129035</v>
       </c>
       <c r="B32" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>129128611</v>
       </c>
       <c r="B33" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129129040</v>
+        <v>129129034</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446141</v>
+        <v>446210</v>
       </c>
       <c r="R34" t="n">
-        <v>6820307</v>
+        <v>6820287</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4009,10 +4009,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129129034</v>
+        <v>129129031</v>
       </c>
       <c r="B35" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446210</v>
+        <v>446212</v>
       </c>
       <c r="R35" t="n">
-        <v>6820287</v>
+        <v>6820334</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4116,10 +4116,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129129031</v>
+        <v>129129036</v>
       </c>
       <c r="B36" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446212</v>
+        <v>446191</v>
       </c>
       <c r="R36" t="n">
-        <v>6820334</v>
+        <v>6820271</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4223,10 +4223,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129129036</v>
+        <v>129129038</v>
       </c>
       <c r="B37" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446191</v>
+        <v>446182</v>
       </c>
       <c r="R37" t="n">
-        <v>6820271</v>
+        <v>6820270</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4330,10 +4330,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129129038</v>
+        <v>129129040</v>
       </c>
       <c r="B38" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4365,10 +4365,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446182</v>
+        <v>446141</v>
       </c>
       <c r="R38" t="n">
-        <v>6820270</v>
+        <v>6820307</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -4009,7 +4009,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129129031</v>
+        <v>129129036</v>
       </c>
       <c r="B35" t="n">
         <v>79041</v>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446212</v>
+        <v>446191</v>
       </c>
       <c r="R35" t="n">
-        <v>6820334</v>
+        <v>6820271</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4116,7 +4116,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129129036</v>
+        <v>129129040</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446191</v>
+        <v>446141</v>
       </c>
       <c r="R36" t="n">
-        <v>6820271</v>
+        <v>6820307</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4223,7 +4223,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129129038</v>
+        <v>129129031</v>
       </c>
       <c r="B37" t="n">
         <v>79041</v>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446182</v>
+        <v>446212</v>
       </c>
       <c r="R37" t="n">
-        <v>6820270</v>
+        <v>6820334</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4330,7 +4330,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129129040</v>
+        <v>129129038</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4365,10 +4365,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446141</v>
+        <v>446182</v>
       </c>
       <c r="R38" t="n">
-        <v>6820307</v>
+        <v>6820270</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -2942,7 +2942,7 @@
         <v>129129058</v>
       </c>
       <c r="B25" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129129040</v>
+        <v>129129038</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446141</v>
+        <v>446182</v>
       </c>
       <c r="R36" t="n">
-        <v>6820307</v>
+        <v>6820270</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4223,7 +4223,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129129031</v>
+        <v>129129040</v>
       </c>
       <c r="B37" t="n">
         <v>79041</v>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446212</v>
+        <v>446141</v>
       </c>
       <c r="R37" t="n">
-        <v>6820334</v>
+        <v>6820307</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4330,7 +4330,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129129038</v>
+        <v>129129031</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4365,10 +4365,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446182</v>
+        <v>446212</v>
       </c>
       <c r="R38" t="n">
-        <v>6820270</v>
+        <v>6820334</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -2942,7 +2942,7 @@
         <v>129129058</v>
       </c>
       <c r="B25" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129129036</v>
+        <v>129129031</v>
       </c>
       <c r="B35" t="n">
         <v>79041</v>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446191</v>
+        <v>446212</v>
       </c>
       <c r="R35" t="n">
-        <v>6820271</v>
+        <v>6820334</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4116,7 +4116,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129129038</v>
+        <v>129129036</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446182</v>
+        <v>446191</v>
       </c>
       <c r="R36" t="n">
-        <v>6820270</v>
+        <v>6820271</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4223,7 +4223,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129129040</v>
+        <v>129129038</v>
       </c>
       <c r="B37" t="n">
         <v>79041</v>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446141</v>
+        <v>446182</v>
       </c>
       <c r="R37" t="n">
-        <v>6820307</v>
+        <v>6820270</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4330,7 +4330,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129129031</v>
+        <v>129129040</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4365,10 +4365,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446212</v>
+        <v>446141</v>
       </c>
       <c r="R38" t="n">
-        <v>6820334</v>
+        <v>6820307</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -3902,7 +3902,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129129034</v>
+        <v>129129031</v>
       </c>
       <c r="B34" t="n">
         <v>79041</v>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446210</v>
+        <v>446212</v>
       </c>
       <c r="R34" t="n">
-        <v>6820287</v>
+        <v>6820334</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4009,7 +4009,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129129031</v>
+        <v>129129038</v>
       </c>
       <c r="B35" t="n">
         <v>79041</v>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446212</v>
+        <v>446182</v>
       </c>
       <c r="R35" t="n">
-        <v>6820334</v>
+        <v>6820270</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4116,7 +4116,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129129036</v>
+        <v>129129034</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446191</v>
+        <v>446210</v>
       </c>
       <c r="R36" t="n">
-        <v>6820271</v>
+        <v>6820287</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4223,7 +4223,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129129038</v>
+        <v>129129036</v>
       </c>
       <c r="B37" t="n">
         <v>79041</v>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446182</v>
+        <v>446191</v>
       </c>
       <c r="R37" t="n">
-        <v>6820270</v>
+        <v>6820271</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -2942,7 +2942,7 @@
         <v>129129058</v>
       </c>
       <c r="B25" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>129129032</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>129128610</v>
       </c>
       <c r="B27" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>129128612</v>
       </c>
       <c r="B28" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>129128613</v>
       </c>
       <c r="B29" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>129129039</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>129129041</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>129129035</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>129128611</v>
       </c>
       <c r="B33" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129129031</v>
+        <v>129129034</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446212</v>
+        <v>446210</v>
       </c>
       <c r="R34" t="n">
-        <v>6820334</v>
+        <v>6820287</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4009,10 +4009,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129129038</v>
+        <v>129129031</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446182</v>
+        <v>446212</v>
       </c>
       <c r="R35" t="n">
-        <v>6820270</v>
+        <v>6820334</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4116,10 +4116,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129129034</v>
+        <v>129129036</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446210</v>
+        <v>446191</v>
       </c>
       <c r="R36" t="n">
-        <v>6820287</v>
+        <v>6820271</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4223,10 +4223,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129129036</v>
+        <v>129129038</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446191</v>
+        <v>446182</v>
       </c>
       <c r="R37" t="n">
-        <v>6820271</v>
+        <v>6820270</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4333,7 +4333,7 @@
         <v>129129040</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 39759-2025 artfynd.xlsx
+++ b/artfynd/A 39759-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128609</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128610</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128611</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128612</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128613</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128615</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1415,6 +1450,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128605463</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129058</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1620,6 +1665,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601920</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1717,6 +1767,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601882</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1814,6 +1869,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601883</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1911,6 +1971,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601884</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2008,6 +2073,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601885</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2105,6 +2175,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601886</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601887</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2299,6 +2379,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601888</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2396,6 +2481,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601889</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2493,6 +2583,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601890</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2590,6 +2685,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601891</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2687,6 +2787,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601892</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2784,6 +2889,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601893</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2881,6 +2991,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601894</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2978,6 +3093,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601895</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3075,6 +3195,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601896</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3172,6 +3297,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601903</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3269,6 +3399,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601904</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3366,6 +3501,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601905</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3473,6 +3613,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129031</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3580,6 +3725,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129032</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3687,6 +3837,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129034</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3794,6 +3949,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129035</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3901,6 +4061,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129036</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4008,6 +4173,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129038</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4115,6 +4285,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129039</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4222,6 +4397,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129040</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4329,6 +4509,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129041</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4436,6 +4621,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129042</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4533,6 +4723,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601875</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4638,6 +4833,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601851</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4743,6 +4943,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601860</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4848,6 +5053,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601862</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4949,6 +5159,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128629754</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5054,6 +5269,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601857</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5151,6 +5371,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601868</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5248,8 +5473,60 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601872</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>